--- a/avatar-apbd/excel/testgsr1.xlsx
+++ b/avatar-apbd/excel/testgsr1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\AVATARAPBD\avatar-apbd\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27D97FB3-9FC6-42E7-BF69-058977185FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E8407D-ED21-48AF-8935-ECDF58318593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{A74FA716-1296-4DAC-A35D-B06376D52DEB}"/>
   </bookViews>
@@ -2716,7 +2716,10 @@
       <c r="V2" s="4">
         <v>3796600</v>
       </c>
-      <c r="W2" s="2"/>
+      <c r="W2" s="2">
+        <f>SUM(V2:V950)</f>
+        <v>604867323936.85022</v>
+      </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -17814,7 +17817,7 @@
         <v>753500</v>
       </c>
     </row>
-    <row r="225" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>6</v>
       </c>
@@ -17882,7 +17885,7 @@
         <v>6894000</v>
       </c>
     </row>
-    <row r="226" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -17950,7 +17953,7 @@
         <v>14400000</v>
       </c>
     </row>
-    <row r="227" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>6</v>
       </c>
@@ -18018,7 +18021,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="228" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -18086,7 +18089,7 @@
         <v>19515000</v>
       </c>
     </row>
-    <row r="229" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>6</v>
       </c>
@@ -18154,7 +18157,7 @@
         <v>2940000</v>
       </c>
     </row>
-    <row r="230" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -18222,7 +18225,7 @@
         <v>5245300</v>
       </c>
     </row>
-    <row r="231" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>6</v>
       </c>
@@ -18290,7 +18293,7 @@
         <v>2250200</v>
       </c>
     </row>
-    <row r="232" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>6</v>
       </c>
@@ -18358,7 +18361,7 @@
         <v>1564950</v>
       </c>
     </row>
-    <row r="233" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -18426,7 +18429,7 @@
         <v>44684500</v>
       </c>
     </row>
-    <row r="234" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>6</v>
       </c>
@@ -18494,7 +18497,7 @@
         <v>77200000</v>
       </c>
     </row>
-    <row r="235" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>6</v>
       </c>
@@ -18562,7 +18565,7 @@
         <v>83000000</v>
       </c>
     </row>
-    <row r="236" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>6</v>
       </c>
@@ -18630,7 +18633,7 @@
         <v>70175000</v>
       </c>
     </row>
-    <row r="237" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>6</v>
       </c>
@@ -18698,7 +18701,7 @@
         <v>5880000</v>
       </c>
     </row>
-    <row r="238" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>6</v>
       </c>
@@ -18766,7 +18769,7 @@
         <v>210000000</v>
       </c>
     </row>
-    <row r="239" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -18833,8 +18836,12 @@
       <c r="V239" s="4">
         <v>2500000</v>
       </c>
-    </row>
-    <row r="240" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W239" s="4">
+        <f>SUM(V239:V950)</f>
+        <v>228468183128.85001</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>6</v>
       </c>
